--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>45.0315</v>
+        <v>77.0489</v>
       </c>
       <c r="E2" t="n">
-        <v>33.9243</v>
+        <v>53.1682</v>
       </c>
       <c r="F2" t="n">
-        <v>11.1073</v>
+        <v>23.8804</v>
       </c>
       <c r="G2" t="n">
-        <v>30.0739</v>
+        <v>46.7363</v>
       </c>
       <c r="H2" t="n">
-        <v>24.9721</v>
+        <v>36.8837</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1014</v>
+        <v>9.8521</v>
       </c>
       <c r="J2" t="n">
-        <v>50.1619</v>
+        <v>65.3925</v>
       </c>
       <c r="K2" t="n">
-        <v>35.4219</v>
+        <v>48.301</v>
       </c>
       <c r="L2" t="n">
-        <v>14.7406</v>
+        <v>17.0916</v>
       </c>
       <c r="M2" t="n">
-        <v>-20.0886</v>
+        <v>-18.6566</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.4498</v>
+        <v>-11.4172</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.6388</v>
+        <v>-7.2395</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.083</v>
+        <v>-3.4143</v>
       </c>
       <c r="Q2" t="n">
-        <v>-52.3985</v>
+        <v>-63.7369</v>
       </c>
       <c r="R2" t="n">
-        <v>48.3157</v>
+        <v>60.3228</v>
       </c>
       <c r="S2" t="n">
-        <v>31.766</v>
+        <v>44.3041</v>
       </c>
       <c r="T2" t="n">
-        <v>19.351</v>
+        <v>28.2555</v>
       </c>
       <c r="U2" t="n">
-        <v>12.4152</v>
+        <v>16.0484</v>
       </c>
       <c r="V2" t="n">
-        <v>-12.7253</v>
+        <v>-10.5767</v>
       </c>
       <c r="W2" t="n">
-        <v>16.8096</v>
+        <v>23.2569</v>
       </c>
       <c r="X2" t="n">
-        <v>-29.5351</v>
+        <v>-33.8334</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>36.2152</v>
+        <v>59.9795</v>
       </c>
       <c r="E3" t="n">
-        <v>20.1218</v>
+        <v>34.8256</v>
       </c>
       <c r="F3" t="n">
-        <v>16.0928</v>
+        <v>25.1541</v>
       </c>
       <c r="G3" t="n">
-        <v>16.1319</v>
+        <v>30.3359</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.0305</v>
+        <v>-7.3283</v>
       </c>
       <c r="I3" t="n">
-        <v>28.1618</v>
+        <v>37.6645</v>
       </c>
       <c r="J3" t="n">
-        <v>47.8458</v>
+        <v>63.5012</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2327</v>
+        <v>4.764600000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>49.0786</v>
+        <v>58.7366</v>
       </c>
       <c r="M3" t="n">
-        <v>-31.7143</v>
+        <v>-33.1651</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.7977</v>
+        <v>-12.0932</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.9167</v>
+        <v>-21.0723</v>
       </c>
       <c r="P3" t="n">
-        <v>-12.7025</v>
+        <v>-15.2513</v>
       </c>
       <c r="Q3" t="n">
-        <v>-61.47179999999999</v>
+        <v>-74.208</v>
       </c>
       <c r="R3" t="n">
-        <v>48.7691</v>
+        <v>58.9564</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2021</v>
+        <v>-4.4801</v>
       </c>
       <c r="T3" t="n">
-        <v>-12.0489</v>
+        <v>-15.7105</v>
       </c>
       <c r="U3" t="n">
-        <v>8.8468</v>
+        <v>11.23</v>
       </c>
       <c r="V3" t="n">
-        <v>35.9881</v>
+        <v>49.3752</v>
       </c>
       <c r="W3" t="n">
-        <v>45.7967</v>
+        <v>61.2426</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.8086</v>
+        <v>-11.8678</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>26.2321</v>
+        <v>16.6969</v>
       </c>
       <c r="E4" t="n">
-        <v>20.9929</v>
+        <v>16.9641</v>
       </c>
       <c r="F4" t="n">
-        <v>5.239000000000001</v>
+        <v>-0.2669999999999997</v>
       </c>
       <c r="G4" t="n">
-        <v>18.7554</v>
+        <v>8.621599999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9.6282</v>
+        <v>7.8758</v>
       </c>
       <c r="I4" t="n">
-        <v>9.1274</v>
+        <v>0.7453000000000013</v>
       </c>
       <c r="J4" t="n">
-        <v>36.8736</v>
+        <v>32.8456</v>
       </c>
       <c r="K4" t="n">
-        <v>20.0822</v>
+        <v>20.894</v>
       </c>
       <c r="L4" t="n">
-        <v>16.7912</v>
+        <v>11.9519</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.118</v>
+        <v>-24.2247</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.4538</v>
+        <v>-13.018</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.664000000000001</v>
+        <v>-11.2063</v>
       </c>
       <c r="P4" t="n">
-        <v>12.2491</v>
+        <v>12.0646</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.6642</v>
+        <v>-40.0634</v>
       </c>
       <c r="R4" t="n">
-        <v>44.9128</v>
+        <v>52.1277</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4383</v>
+        <v>6.037500000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9537</v>
+        <v>-1.078800000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>6.3917</v>
+        <v>7.1169</v>
       </c>
       <c r="V4" t="n">
-        <v>-9.210799999999999</v>
+        <v>-10.0266</v>
       </c>
       <c r="W4" t="n">
-        <v>18.7367</v>
+        <v>25.2604</v>
       </c>
       <c r="X4" t="n">
-        <v>-27.9474</v>
+        <v>-35.2872</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>17.762</v>
+        <v>10.8361</v>
       </c>
       <c r="E5" t="n">
-        <v>10.2747</v>
+        <v>3.546400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>7.487400000000001</v>
+        <v>7.2896</v>
       </c>
       <c r="G5" t="n">
-        <v>24.3291</v>
+        <v>15.77</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6915</v>
+        <v>1.9064</v>
       </c>
       <c r="I5" t="n">
-        <v>16.6378</v>
+        <v>13.8639</v>
       </c>
       <c r="J5" t="n">
-        <v>30.0207</v>
+        <v>25.9662</v>
       </c>
       <c r="K5" t="n">
-        <v>18.6604</v>
+        <v>16.186</v>
       </c>
       <c r="L5" t="n">
-        <v>11.3611</v>
+        <v>9.780200000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.6918</v>
+        <v>-10.196</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.9685</v>
+        <v>-14.2795</v>
       </c>
       <c r="O5" t="n">
-        <v>5.2767</v>
+        <v>4.0839</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6806000000000003</v>
+        <v>7.7397</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.747</v>
+        <v>-38.4696</v>
       </c>
       <c r="R5" t="n">
-        <v>37.4276</v>
+        <v>46.2096</v>
       </c>
       <c r="S5" t="n">
-        <v>-17.6472</v>
+        <v>-22.986</v>
       </c>
       <c r="T5" t="n">
-        <v>-11.4411</v>
+        <v>-15.101</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.205900000000001</v>
+        <v>-7.885</v>
       </c>
       <c r="V5" t="n">
-        <v>10.3993</v>
+        <v>10.3124</v>
       </c>
       <c r="W5" t="n">
-        <v>28.4419</v>
+        <v>31.1513</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.0426</v>
+        <v>-20.8389</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0123</v>
+        <v>3.5462</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6133</v>
+        <v>0.7729999999999997</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3988</v>
+        <v>2.773500000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.507400000000001</v>
+        <v>-3.3751</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3696</v>
+        <v>-1.9481</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.138</v>
+        <v>-1.4267</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5753</v>
+        <v>2.0087</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5404</v>
+        <v>2.5081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03459999999999998</v>
+        <v>-0.4998</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.0827</v>
+        <v>-5.3838</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.9101</v>
+        <v>-4.4562</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1725</v>
+        <v>-0.9271999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>5.444100000000001</v>
+        <v>5.4633</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>6.805000000000001</v>
+        <v>8.194900000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>5.0965</v>
+        <v>4.4823</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9811</v>
+        <v>1.0939</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1153</v>
+        <v>3.3887</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.0209</v>
+        <v>-3.0244</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4180000000000001</v>
+        <v>0.4018999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>A. ZECEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2679</v>
+        <v>-0.1724</v>
       </c>
       <c r="E7" t="n">
-        <v>4.186599999999999</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08099999999999952</v>
+        <v>-0.1724</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8892</v>
+        <v>-0.1724</v>
       </c>
       <c r="H7" t="n">
-        <v>3.721</v>
+        <v>-0.1724</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.610200000000001</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12.6236</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10.1024</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5214</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-14.5131</v>
+        <v>-0.1724</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.3816</v>
+        <v>-0.1724</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.1313</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5879</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-29.0347</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>27.4467</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>15.0078</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>10.474</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.5339</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.263199999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>10.1235</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ZECEVIC</t>
+          <t>B. ERRASTI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1732</v>
+        <v>-0.3592</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1732</v>
+        <v>-0.2895</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1732</v>
+        <v>-0.04339999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1732</v>
+        <v>-0.2013</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,31 +1060,31 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1732</v>
+        <v>-0.04339999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.2013</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.5435</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.4738</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. ERRASTI</t>
+          <t>K. DE CASTRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3623</v>
+        <v>-1.5327</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0696</v>
+        <v>0.0172</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2927</v>
+        <v>-1.5499</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.1972</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.205</v>
+        <v>0.1752</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1573</v>
+        <v>-0.3724</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.2144</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.205</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5414</v>
+        <v>-0.0882</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4718</v>
+        <v>-0.0882</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. DE CASTRO</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5397</v>
+        <v>-2.852800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0173</v>
+        <v>2.5138</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.557</v>
+        <v>-5.3665</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1986</v>
+        <v>-5.128299999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1746</v>
+        <v>3.7078</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3732</v>
+        <v>-8.836399999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0173</v>
+        <v>14.3413</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>12.1237</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.2176</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2159</v>
+        <v>-19.4695</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1573</v>
+        <v>-8.4156</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-11.0538</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.8208</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-33.6898</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>31.8684</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0877</v>
+        <v>16.6257</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>11.7118</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0877</v>
+        <v>4.9145</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-12.5286</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>10.1506</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-22.6795</v>
       </c>
     </row>
     <row r="11">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.239899999999999</v>
+        <v>-10.5202</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.018000000000001</v>
+        <v>-14.5233</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2216999999999996</v>
+        <v>4.0033</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0508</v>
+        <v>-4.8056</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.2339</v>
+        <v>-4.7887</v>
       </c>
       <c r="I11" t="n">
-        <v>2.183000000000001</v>
+        <v>-0.01659999999999995</v>
       </c>
       <c r="J11" t="n">
-        <v>15.8657</v>
+        <v>16.029</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8432</v>
+        <v>10.3321</v>
       </c>
       <c r="L11" t="n">
-        <v>11.0225</v>
+        <v>5.697299999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.9165</v>
+        <v>-20.8349</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.0771</v>
+        <v>-15.1206</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.8392</v>
+        <v>-5.7138</v>
       </c>
       <c r="P11" t="n">
-        <v>11.5684</v>
+        <v>13.4303</v>
       </c>
       <c r="Q11" t="n">
-        <v>-31.7568</v>
+        <v>-39.3805</v>
       </c>
       <c r="R11" t="n">
-        <v>43.3253</v>
+        <v>52.8109</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.385100000000001</v>
+        <v>-9.302299999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.1107</v>
+        <v>-7.6866</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.2742</v>
+        <v>-1.6152</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.3722</v>
+        <v>-9.842600000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>12.9838</v>
+        <v>16.5147</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.356</v>
+        <v>-26.3573</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.6502</v>
+        <v>-18.9246</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.1447</v>
+        <v>-16.7783</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5056</v>
+        <v>-2.1465</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.1781</v>
+        <v>-17.9243</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.8781</v>
+        <v>-8.3245</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.2997</v>
+        <v>-9.5999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6823</v>
+        <v>-1.2372</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5709999999999997</v>
+        <v>-0.1976000000000006</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2531</v>
+        <v>-1.0396</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.4961</v>
+        <v>-16.6872</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.449300000000001</v>
+        <v>-8.127000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.0469</v>
+        <v>-8.5603</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4024</v>
+        <v>5.0078</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.5077</v>
+        <v>-21.3975</v>
       </c>
       <c r="R12" t="n">
-        <v>22.9102</v>
+        <v>26.4055</v>
       </c>
       <c r="S12" t="n">
-        <v>7.6655</v>
+        <v>7.722899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8312</v>
+        <v>2.501499999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>4.8343</v>
+        <v>5.2212</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.5401</v>
+        <v>-13.7309</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2138</v>
+        <v>3.3549</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.754</v>
+        <v>-17.0856</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.4908</v>
+        <v>-25.9706</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.1549</v>
+        <v>-11.0659</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.3361</v>
+        <v>-14.9049</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.154500000000001</v>
+        <v>-8.066600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1222</v>
+        <v>-0.6930000000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0327</v>
+        <v>-7.373699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5551</v>
+        <v>5.707299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0795</v>
+        <v>5.0756</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4758999999999997</v>
+        <v>0.6315999999999995</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.7098</v>
+        <v>-13.7742</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.2011</v>
+        <v>-5.7686</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.5084</v>
+        <v>-8.005599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>9.3001</v>
+        <v>7.9672</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2074</v>
+        <v>-16.1619</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5075</v>
+        <v>24.129</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5106</v>
+        <v>-4.3822</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6632</v>
+        <v>-1.8586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8474999999999999</v>
+        <v>-2.5237</v>
       </c>
       <c r="V13" t="n">
-        <v>-18.1256</v>
+        <v>-21.4888</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>1.2473</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.2863</v>
+        <v>-22.7361</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.9699</v>
+        <v>-34.367</v>
       </c>
       <c r="E14" t="n">
-        <v>-28.2672</v>
+        <v>-41.6151</v>
       </c>
       <c r="F14" t="n">
-        <v>1.297600000000001</v>
+        <v>7.2482</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.878</v>
+        <v>-15.2025</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.8129</v>
+        <v>-6.0084</v>
       </c>
       <c r="I14" t="n">
-        <v>-11.0655</v>
+        <v>-9.193899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5245</v>
+        <v>6.8081</v>
       </c>
       <c r="K14" t="n">
-        <v>8.3794</v>
+        <v>7.818000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.854900000000001</v>
+        <v>-1.010000000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.4023</v>
+        <v>-22.0108</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.192</v>
+        <v>-13.8266</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.2103</v>
+        <v>-8.184000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1341</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-45.3665</v>
+        <v>-56.2251</v>
       </c>
       <c r="R14" t="n">
-        <v>46.501</v>
+        <v>55.0871</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.0513</v>
+        <v>-19.4349</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.5722</v>
+        <v>-13.3297</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.4795</v>
+        <v>-6.1047</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8257</v>
+        <v>1.408400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>21.147</v>
+        <v>21.1318</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.3212</v>
+        <v>-19.7231</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>-44.8091</v>
+        <v>-48.4355</v>
       </c>
       <c r="E15" t="n">
-        <v>-45.8709</v>
+        <v>-54.9781</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0618</v>
+        <v>6.5425</v>
       </c>
       <c r="G15" t="n">
-        <v>-21.7098</v>
+        <v>-18.7641</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.4808</v>
+        <v>-12.8426</v>
       </c>
       <c r="I15" t="n">
-        <v>-11.2291</v>
+        <v>-5.9216</v>
       </c>
       <c r="J15" t="n">
-        <v>6.396399999999998</v>
+        <v>11.5176</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7986</v>
+        <v>5.079100000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5979</v>
+        <v>6.438599999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-28.1062</v>
+        <v>-30.282</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.2791</v>
+        <v>-17.9221</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.8269</v>
+        <v>-12.3599</v>
       </c>
       <c r="P15" t="n">
-        <v>-25.6322</v>
+        <v>-33.4621</v>
       </c>
       <c r="Q15" t="n">
-        <v>-74.4011</v>
+        <v>-93.5564</v>
       </c>
       <c r="R15" t="n">
-        <v>48.769</v>
+        <v>60.0945</v>
       </c>
       <c r="S15" t="n">
-        <v>-11.8457</v>
+        <v>-18.1079</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.3933</v>
+        <v>-14.7706</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.4522</v>
+        <v>-3.337</v>
       </c>
       <c r="V15" t="n">
-        <v>14.3782</v>
+        <v>21.8983</v>
       </c>
       <c r="W15" t="n">
-        <v>31.5272</v>
+        <v>41.83150000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-17.1491</v>
+        <v>-19.9328</v>
       </c>
     </row>
     <row r="16">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>-50.9257</v>
+        <v>-54.279</v>
       </c>
       <c r="E16" t="n">
-        <v>-54.9419</v>
+        <v>-57.8853</v>
       </c>
       <c r="F16" t="n">
-        <v>4.015600000000001</v>
+        <v>3.605799999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-30.8451</v>
+        <v>-31.2022</v>
       </c>
       <c r="H16" t="n">
-        <v>-25.6988</v>
+        <v>-27.7926</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.1465</v>
+        <v>-3.409199999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.643</v>
+        <v>-7.4983</v>
       </c>
       <c r="K16" t="n">
-        <v>-16.9663</v>
+        <v>-15.5574</v>
       </c>
       <c r="L16" t="n">
-        <v>6.3236</v>
+        <v>8.0595</v>
       </c>
       <c r="M16" t="n">
-        <v>-20.2024</v>
+        <v>-23.7036</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.7325</v>
+        <v>-12.2347</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.4701</v>
+        <v>-11.469</v>
       </c>
       <c r="P16" t="n">
-        <v>-12.476</v>
+        <v>-7.0568</v>
       </c>
       <c r="Q16" t="n">
-        <v>-59.8841</v>
+        <v>-65.5579</v>
       </c>
       <c r="R16" t="n">
-        <v>47.4083</v>
+        <v>58.5015</v>
       </c>
       <c r="S16" t="n">
-        <v>-25.8135</v>
+        <v>-34.7331</v>
       </c>
       <c r="T16" t="n">
-        <v>-19.7342</v>
+        <v>-25.0823</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.0795</v>
+        <v>-9.650700000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>18.209</v>
+        <v>18.7127</v>
       </c>
       <c r="W16" t="n">
-        <v>35.3193</v>
+        <v>40.254</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.1105</v>
+        <v>-21.5415</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-36.63980000000001</v>
+        <v>-29.3064</v>
       </c>
       <c r="E17" t="n">
-        <v>-68.33629999999998</v>
+        <v>-85.10740000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>31.695</v>
+        <v>55.80070000000002</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.34210000000001</v>
+        <v>-3.417900000000007</v>
       </c>
       <c r="H17" t="n">
-        <v>-24.8176</v>
+        <v>-19.551</v>
       </c>
       <c r="I17" t="n">
-        <v>12.4738</v>
+        <v>16.13330000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>198.1346</v>
+        <v>235.3992</v>
       </c>
       <c r="K17" t="n">
-        <v>89.29729999999999</v>
+        <v>117.3444</v>
       </c>
       <c r="L17" t="n">
-        <v>108.8394</v>
+        <v>118.0555</v>
       </c>
       <c r="M17" t="n">
-        <v>-210.4786</v>
+        <v>-238.8186</v>
       </c>
       <c r="N17" t="n">
-        <v>-114.1135</v>
+        <v>-136.8951</v>
       </c>
       <c r="O17" t="n">
-        <v>-96.36429999999999</v>
+        <v>-101.9223</v>
       </c>
       <c r="P17" t="n">
-        <v>-12.476</v>
+        <v>-10.243</v>
       </c>
       <c r="Q17" t="n">
-        <v>-454.8007999999999</v>
+        <v>-545.1786</v>
       </c>
       <c r="R17" t="n">
-        <v>442.325</v>
+        <v>534.9359000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-21.1105</v>
+        <v>-34.88570000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-36.3496</v>
+        <v>-51.1251</v>
       </c>
       <c r="U17" t="n">
-        <v>15.23889999999999</v>
+        <v>16.2414</v>
       </c>
       <c r="V17" t="n">
-        <v>9.288799999999998</v>
+        <v>19.2412</v>
       </c>
       <c r="W17" t="n">
-        <v>224.6782</v>
+        <v>275.7979</v>
       </c>
       <c r="X17" t="n">
-        <v>-215.3898</v>
+        <v>-256.5565999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>77.0489</v>
+        <v>67.5339</v>
       </c>
       <c r="E2" t="n">
-        <v>53.1682</v>
+        <v>43.9671</v>
       </c>
       <c r="F2" t="n">
-        <v>23.8804</v>
+        <v>23.5662</v>
       </c>
       <c r="G2" t="n">
-        <v>46.7363</v>
+        <v>30.3359</v>
       </c>
       <c r="H2" t="n">
-        <v>36.8837</v>
+        <v>-7.3283</v>
       </c>
       <c r="I2" t="n">
-        <v>9.8521</v>
+        <v>37.6645</v>
       </c>
       <c r="J2" t="n">
-        <v>65.3925</v>
+        <v>63.5012</v>
       </c>
       <c r="K2" t="n">
-        <v>48.301</v>
+        <v>4.764600000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>17.0916</v>
+        <v>58.7366</v>
       </c>
       <c r="M2" t="n">
-        <v>-18.6566</v>
+        <v>-33.1651</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.4172</v>
+        <v>-12.0932</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.2395</v>
+        <v>-21.0723</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.4143</v>
+        <v>-15.2513</v>
       </c>
       <c r="Q2" t="n">
-        <v>-63.7369</v>
+        <v>-74.208</v>
       </c>
       <c r="R2" t="n">
-        <v>60.3228</v>
+        <v>58.9564</v>
       </c>
       <c r="S2" t="n">
-        <v>44.3041</v>
+        <v>3.0741</v>
       </c>
       <c r="T2" t="n">
-        <v>28.2555</v>
+        <v>-6.5689</v>
       </c>
       <c r="U2" t="n">
-        <v>16.0484</v>
+        <v>9.6424</v>
       </c>
       <c r="V2" t="n">
-        <v>-10.5767</v>
+        <v>49.3752</v>
       </c>
       <c r="W2" t="n">
-        <v>23.2569</v>
+        <v>61.2426</v>
       </c>
       <c r="X2" t="n">
-        <v>-33.8334</v>
+        <v>-11.8678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>59.9795</v>
+        <v>47.3173</v>
       </c>
       <c r="E3" t="n">
-        <v>34.8256</v>
+        <v>30.037</v>
       </c>
       <c r="F3" t="n">
-        <v>25.1541</v>
+        <v>17.2801</v>
       </c>
       <c r="G3" t="n">
-        <v>30.3359</v>
+        <v>46.7363</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.3283</v>
+        <v>36.8837</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6645</v>
+        <v>9.8521</v>
       </c>
       <c r="J3" t="n">
-        <v>63.5012</v>
+        <v>65.3925</v>
       </c>
       <c r="K3" t="n">
-        <v>4.764600000000001</v>
+        <v>48.301</v>
       </c>
       <c r="L3" t="n">
-        <v>58.7366</v>
+        <v>17.0916</v>
       </c>
       <c r="M3" t="n">
-        <v>-33.1651</v>
+        <v>-18.6566</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.0932</v>
+        <v>-11.4172</v>
       </c>
       <c r="O3" t="n">
-        <v>-21.0723</v>
+        <v>-7.2395</v>
       </c>
       <c r="P3" t="n">
-        <v>-15.2513</v>
+        <v>-3.4143</v>
       </c>
       <c r="Q3" t="n">
-        <v>-74.208</v>
+        <v>-63.7369</v>
       </c>
       <c r="R3" t="n">
-        <v>58.9564</v>
+        <v>60.3228</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.4801</v>
+        <v>14.5718</v>
       </c>
       <c r="T3" t="n">
-        <v>-15.7105</v>
+        <v>5.1244</v>
       </c>
       <c r="U3" t="n">
-        <v>11.23</v>
+        <v>9.447900000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>49.3752</v>
+        <v>-10.5767</v>
       </c>
       <c r="W3" t="n">
-        <v>61.2426</v>
+        <v>23.2569</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.8678</v>
+        <v>-33.8334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6969</v>
+        <v>24.9608</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9641</v>
+        <v>11.9846</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2669999999999997</v>
+        <v>12.9766</v>
       </c>
       <c r="G4" t="n">
-        <v>8.621599999999999</v>
+        <v>15.77</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8758</v>
+        <v>1.9064</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7453000000000013</v>
+        <v>13.8639</v>
       </c>
       <c r="J4" t="n">
-        <v>32.8456</v>
+        <v>25.9662</v>
       </c>
       <c r="K4" t="n">
-        <v>20.894</v>
+        <v>16.186</v>
       </c>
       <c r="L4" t="n">
-        <v>11.9519</v>
+        <v>9.780200000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-24.2247</v>
+        <v>-10.196</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.018</v>
+        <v>-14.2795</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.2063</v>
+        <v>4.0839</v>
       </c>
       <c r="P4" t="n">
-        <v>12.0646</v>
+        <v>7.7397</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40.0634</v>
+        <v>-38.4696</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1277</v>
+        <v>46.2096</v>
       </c>
       <c r="S4" t="n">
-        <v>6.037500000000001</v>
+        <v>-8.8612</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.078800000000001</v>
+        <v>-6.6631</v>
       </c>
       <c r="U4" t="n">
-        <v>7.1169</v>
+        <v>-2.1979</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.0266</v>
+        <v>10.3124</v>
       </c>
       <c r="W4" t="n">
-        <v>25.2604</v>
+        <v>31.1513</v>
       </c>
       <c r="X4" t="n">
-        <v>-35.2872</v>
+        <v>-20.8389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>10.8361</v>
+        <v>15.3459</v>
       </c>
       <c r="E5" t="n">
-        <v>3.546400000000001</v>
+        <v>16.6089</v>
       </c>
       <c r="F5" t="n">
-        <v>7.2896</v>
+        <v>-1.262900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>15.77</v>
+        <v>8.621599999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9064</v>
+        <v>7.8758</v>
       </c>
       <c r="I5" t="n">
-        <v>13.8639</v>
+        <v>0.7453000000000013</v>
       </c>
       <c r="J5" t="n">
-        <v>25.9662</v>
+        <v>32.8456</v>
       </c>
       <c r="K5" t="n">
-        <v>16.186</v>
+        <v>20.894</v>
       </c>
       <c r="L5" t="n">
-        <v>9.780200000000001</v>
+        <v>11.9519</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.196</v>
+        <v>-24.2247</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.2795</v>
+        <v>-13.018</v>
       </c>
       <c r="O5" t="n">
-        <v>4.0839</v>
+        <v>-11.2063</v>
       </c>
       <c r="P5" t="n">
-        <v>7.7397</v>
+        <v>12.0646</v>
       </c>
       <c r="Q5" t="n">
-        <v>-38.4696</v>
+        <v>-40.0634</v>
       </c>
       <c r="R5" t="n">
-        <v>46.2096</v>
+        <v>52.1277</v>
       </c>
       <c r="S5" t="n">
-        <v>-22.986</v>
+        <v>4.6868</v>
       </c>
       <c r="T5" t="n">
-        <v>-15.101</v>
+        <v>-1.434</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.885</v>
+        <v>6.1208</v>
       </c>
       <c r="V5" t="n">
-        <v>10.3124</v>
+        <v>-10.0266</v>
       </c>
       <c r="W5" t="n">
-        <v>31.1513</v>
+        <v>25.2604</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.8389</v>
+        <v>-35.2872</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5462</v>
+        <v>1.5835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7729999999999997</v>
+        <v>-0.8156999999999996</v>
       </c>
       <c r="F6" t="n">
-        <v>2.773500000000001</v>
+        <v>2.3995</v>
       </c>
       <c r="G6" t="n">
         <v>-3.3751</v>
@@ -922,13 +922,13 @@
         <v>8.194900000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4823</v>
+        <v>2.5197</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0939</v>
+        <v>-0.4948</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3887</v>
+        <v>3.0144</v>
       </c>
       <c r="V6" t="n">
         <v>-3.0244</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5327</v>
+        <v>-1.4142</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0172</v>
+        <v>0.1357</v>
       </c>
       <c r="F9" t="n">
         <v>-1.5499</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0882</v>
+        <v>0.0302</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0882</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.852800000000001</v>
+        <v>-5.727100000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5138</v>
+        <v>-12.5999</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.3665</v>
+        <v>6.872400000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.128299999999999</v>
+        <v>-4.8056</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7078</v>
+        <v>-4.7887</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.836399999999999</v>
+        <v>-0.01659999999999995</v>
       </c>
       <c r="J10" t="n">
-        <v>14.3413</v>
+        <v>16.029</v>
       </c>
       <c r="K10" t="n">
-        <v>12.1237</v>
+        <v>10.3321</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2176</v>
+        <v>5.697299999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-19.4695</v>
+        <v>-20.8349</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.4156</v>
+        <v>-15.1206</v>
       </c>
       <c r="O10" t="n">
-        <v>-11.0538</v>
+        <v>-5.7138</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8208</v>
+        <v>13.4303</v>
       </c>
       <c r="Q10" t="n">
-        <v>-33.6898</v>
+        <v>-39.3805</v>
       </c>
       <c r="R10" t="n">
-        <v>31.8684</v>
+        <v>52.8109</v>
       </c>
       <c r="S10" t="n">
-        <v>16.6257</v>
+        <v>-4.509</v>
       </c>
       <c r="T10" t="n">
-        <v>11.7118</v>
+        <v>-5.7633</v>
       </c>
       <c r="U10" t="n">
-        <v>4.9145</v>
+        <v>1.2543</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.5286</v>
+        <v>-9.842600000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>10.1506</v>
+        <v>16.5147</v>
       </c>
       <c r="X10" t="n">
-        <v>-22.6795</v>
+        <v>-26.3573</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.5202</v>
+        <v>-16.84</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.5233</v>
+        <v>-8.153200000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0033</v>
+        <v>-8.687099999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8056</v>
+        <v>-5.128299999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.7887</v>
+        <v>3.7078</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01659999999999995</v>
+        <v>-8.836399999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>16.029</v>
+        <v>14.3413</v>
       </c>
       <c r="K11" t="n">
-        <v>10.3321</v>
+        <v>12.1237</v>
       </c>
       <c r="L11" t="n">
-        <v>5.697299999999999</v>
+        <v>2.2176</v>
       </c>
       <c r="M11" t="n">
-        <v>-20.8349</v>
+        <v>-19.4695</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.1206</v>
+        <v>-8.4156</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.7138</v>
+        <v>-11.0538</v>
       </c>
       <c r="P11" t="n">
-        <v>13.4303</v>
+        <v>-1.8208</v>
       </c>
       <c r="Q11" t="n">
-        <v>-39.3805</v>
+        <v>-33.6898</v>
       </c>
       <c r="R11" t="n">
-        <v>52.8109</v>
+        <v>31.8684</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.302299999999999</v>
+        <v>2.6384</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.6866</v>
+        <v>1.0448</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6152</v>
+        <v>1.5937</v>
       </c>
       <c r="V11" t="n">
-        <v>-9.842600000000001</v>
+        <v>-12.5286</v>
       </c>
       <c r="W11" t="n">
-        <v>16.5147</v>
+        <v>10.1506</v>
       </c>
       <c r="X11" t="n">
-        <v>-26.3573</v>
+        <v>-22.6795</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.9246</v>
+        <v>-21.5085</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.7783</v>
+        <v>-18.5198</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1465</v>
+        <v>-2.9889</v>
       </c>
       <c r="G12" t="n">
         <v>-17.9243</v>
@@ -1390,13 +1390,13 @@
         <v>26.4055</v>
       </c>
       <c r="S12" t="n">
-        <v>7.722899999999999</v>
+        <v>5.1387</v>
       </c>
       <c r="T12" t="n">
-        <v>2.501499999999999</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2212</v>
+        <v>4.3786</v>
       </c>
       <c r="V12" t="n">
         <v>-13.7309</v>
@@ -1423,13 +1423,13 @@
         <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.9706</v>
+        <v>-21.8259</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.0659</v>
+        <v>-10.1253</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.9049</v>
+        <v>-11.701</v>
       </c>
       <c r="G13" t="n">
         <v>-8.066600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>24.129</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3822</v>
+        <v>-0.2375</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8586</v>
+        <v>-0.9179</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5237</v>
+        <v>0.6803</v>
       </c>
       <c r="V13" t="n">
         <v>-21.4888</v>
@@ -1501,13 +1501,13 @@
         <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.367</v>
+        <v>-23.7413</v>
       </c>
       <c r="E14" t="n">
-        <v>-41.6151</v>
+        <v>-36.4938</v>
       </c>
       <c r="F14" t="n">
-        <v>7.2482</v>
+        <v>12.7524</v>
       </c>
       <c r="G14" t="n">
         <v>-15.2025</v>
@@ -1546,13 +1546,13 @@
         <v>55.0871</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.4349</v>
+        <v>-8.8085</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.3297</v>
+        <v>-8.2082</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.1047</v>
+        <v>-0.6007999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.408400000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-48.4355</v>
+        <v>-28.0786</v>
       </c>
       <c r="E15" t="n">
-        <v>-54.9781</v>
+        <v>-42.1103</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5425</v>
+        <v>14.0315</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.7641</v>
+        <v>-31.2022</v>
       </c>
       <c r="H15" t="n">
-        <v>-12.8426</v>
+        <v>-27.7926</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.9216</v>
+        <v>-3.409199999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>11.5176</v>
+        <v>-7.4983</v>
       </c>
       <c r="K15" t="n">
-        <v>5.079100000000001</v>
+        <v>-15.5574</v>
       </c>
       <c r="L15" t="n">
-        <v>6.438599999999999</v>
+        <v>8.0595</v>
       </c>
       <c r="M15" t="n">
-        <v>-30.282</v>
+        <v>-23.7036</v>
       </c>
       <c r="N15" t="n">
-        <v>-17.9221</v>
+        <v>-12.2347</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.3599</v>
+        <v>-11.469</v>
       </c>
       <c r="P15" t="n">
-        <v>-33.4621</v>
+        <v>-7.0568</v>
       </c>
       <c r="Q15" t="n">
-        <v>-93.5564</v>
+        <v>-65.5579</v>
       </c>
       <c r="R15" t="n">
-        <v>60.0945</v>
+        <v>58.5015</v>
       </c>
       <c r="S15" t="n">
-        <v>-18.1079</v>
+        <v>-8.5329</v>
       </c>
       <c r="T15" t="n">
-        <v>-14.7706</v>
+        <v>-9.308199999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.337</v>
+        <v>0.7750000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>21.8983</v>
+        <v>18.7127</v>
       </c>
       <c r="W15" t="n">
-        <v>41.83150000000001</v>
+        <v>40.254</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.9328</v>
+        <v>-21.5415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-54.279</v>
+        <v>-37.8558</v>
       </c>
       <c r="E16" t="n">
-        <v>-57.8853</v>
+        <v>-47.801</v>
       </c>
       <c r="F16" t="n">
-        <v>3.605799999999999</v>
+        <v>9.945499999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-31.2022</v>
+        <v>-18.7641</v>
       </c>
       <c r="H16" t="n">
-        <v>-27.7926</v>
+        <v>-12.8426</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.409199999999999</v>
+        <v>-5.9216</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.4983</v>
+        <v>11.5176</v>
       </c>
       <c r="K16" t="n">
-        <v>-15.5574</v>
+        <v>5.079100000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>8.0595</v>
+        <v>6.438599999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-23.7036</v>
+        <v>-30.282</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.2347</v>
+        <v>-17.9221</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.469</v>
+        <v>-12.3599</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.0568</v>
+        <v>-33.4621</v>
       </c>
       <c r="Q16" t="n">
-        <v>-65.5579</v>
+        <v>-93.5564</v>
       </c>
       <c r="R16" t="n">
-        <v>58.5015</v>
+        <v>60.0945</v>
       </c>
       <c r="S16" t="n">
-        <v>-34.7331</v>
+        <v>-7.527600000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-25.0823</v>
+        <v>-7.593599999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-9.650700000000001</v>
+        <v>0.06590000000000018</v>
       </c>
       <c r="V16" t="n">
-        <v>18.7127</v>
+        <v>21.8983</v>
       </c>
       <c r="W16" t="n">
-        <v>40.254</v>
+        <v>41.83150000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-21.5415</v>
+        <v>-19.9328</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-29.3064</v>
+        <v>-0.7815999999999903</v>
       </c>
       <c r="E17" t="n">
-        <v>-85.10740000000001</v>
+        <v>-73.95540000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>55.80070000000002</v>
+        <v>73.1725</v>
       </c>
       <c r="G17" t="n">
         <v>-3.417900000000007</v>
@@ -1780,13 +1780,13 @@
         <v>534.9359000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-34.88570000000001</v>
+        <v>-6.360500000000006</v>
       </c>
       <c r="T17" t="n">
-        <v>-51.1251</v>
+        <v>-39.9741</v>
       </c>
       <c r="U17" t="n">
-        <v>16.2414</v>
+        <v>33.6126</v>
       </c>
       <c r="V17" t="n">
         <v>19.2412</v>
